--- a/tame_output/ON/bt/strategyON_20230810.xlsx
+++ b/tame_output/ON/bt/strategyON_20230810.xlsx
@@ -595,7 +595,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -623,12 +623,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -652,7 +652,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -736,7 +736,7 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>65.7%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>82.9%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -758,16 +758,16 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>2.82</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>59.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -776,7 +776,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.9%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -829,7 +829,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -839,12 +839,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>69.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -889,7 +889,7 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>14.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
     </row>
@@ -901,12 +901,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -920,7 +920,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>11.7%</t>
         </is>
       </c>
     </row>
@@ -1054,7 +1054,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>107.9%</t>
+          <t>107.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.37</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1073,7 +1073,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-2.6%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>103.7%</t>
+          <t>103.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1195,7 +1195,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>17.8%</t>
         </is>
       </c>
     </row>
@@ -1207,7 +1207,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>55.5%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1226,7 +1226,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>70.8%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1360,7 +1360,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>140.6%</t>
+          <t>140.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1370,7 +1370,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.30</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1379,7 +1379,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2023-08-08</t>
+          <t>2023-08-09</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>33.2%</t>
+          <t>33.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1431,17 +1431,17 @@
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>135.1%</t>
+          <t>134.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>17.8%</t>
         </is>
       </c>
     </row>
@@ -1516,7 +1516,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1684"/>
+  <dimension ref="A1:G1685"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -40242,7 +40242,7 @@
         <v>45146</v>
       </c>
       <c r="B1684" t="n">
-        <v>2.89623914745492</v>
+        <v>2.896173040448571</v>
       </c>
       <c r="C1684" t="n">
         <v>2.995206865393437</v>
@@ -40258,6 +40258,29 @@
       </c>
       <c r="G1684" t="n">
         <v>4.297246066579779</v>
+      </c>
+    </row>
+    <row r="1685">
+      <c r="A1685" s="2" t="n">
+        <v>45147</v>
+      </c>
+      <c r="B1685" t="n">
+        <v>2.892115293780109</v>
+      </c>
+      <c r="C1685" t="n">
+        <v>2.986657920131648</v>
+      </c>
+      <c r="D1685" t="n">
+        <v>1.541176246833767</v>
+      </c>
+      <c r="E1685" t="n">
+        <v>3.602771994551409</v>
+      </c>
+      <c r="F1685" t="n">
+        <v>2.169422925440184</v>
+      </c>
+      <c r="G1685" t="n">
+        <v>4.28831167539576</v>
       </c>
     </row>
   </sheetData>
